--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.29.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.29.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -839,7 +839,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.29.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.29.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -597,16 +597,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L2: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: satisfy the Courtâ€”â€”</t>
+          <t>L102: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L4: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: satisfy the Courtâ€”</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]THE BILL.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]THE BILL.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L15: isolated marker/symbol line :: 0</t>
@@ -641,7 +645,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -650,14 +654,10 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L71: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ee post under head of â€œSpeeding the</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L44: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: held irregular.â€”(King of Spain vs. Hullett, 3 Sim.</t>
+          <t>L110: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -705,16 +705,8 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L102: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L110: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
@@ -724,7 +716,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L110: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L110: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -746,12 +738,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -760,17 +752,13 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L108: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: held irregular.â€”(King of</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L102: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L102: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
@@ -811,11 +799,7 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L119: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ar.â€”(King of Spain vs. Hullett, 3 Sim.</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
@@ -969,12 +953,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1013,7 +997,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
